--- a/GenAI - MRM Practices.xlsx
+++ b/GenAI - MRM Practices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/481edc4588b61275/AI_Research/2025/GenAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="907" documentId="8_{DB147ED1-99E2-483C-9EC2-FF9E9E36544C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3F1B502-EFD2-4F95-A2E4-41C7DC8EAFE8}"/>
+  <xr:revisionPtr revIDLastSave="933" documentId="8_{DB147ED1-99E2-483C-9EC2-FF9E9E36544C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CE3729E-4803-4CC5-802B-C56EC906EB0B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="738" xr2:uid="{76905005-ACFB-44FC-8D05-AE4BBA0544CF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="738" activeTab="8" xr2:uid="{76905005-ACFB-44FC-8D05-AE4BBA0544CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Terminology" sheetId="7" r:id="rId1"/>
@@ -24,7 +24,6 @@
     <sheet name="Ref" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="453">
   <si>
     <t>GenAI usage categories and examples</t>
   </si>
@@ -324,9 +323,6 @@
   </si>
   <si>
     <t>Judging LLM-as-a-Judge with MT-Bench and Chatbot Arena</t>
-  </si>
-  <si>
-    <t>provides a practical solution for evaluating LLMs using the LLM-as-a-Judge approach with Amazon Bedrock.</t>
   </si>
   <si>
     <t>https://github.com/quotient-ai/judges</t>
@@ -2165,6 +2161,42 @@
   </si>
   <si>
     <t>Key References:</t>
+  </si>
+  <si>
+    <t>Model Validation Practice in Banking: A Structured Approach for Predictive Models</t>
+  </si>
+  <si>
+    <t>Model Validation Practice in Banking</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2410.13877</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile</t>
+  </si>
+  <si>
+    <t>NIST: Artificial Intelligence Risk Management Framework</t>
+  </si>
+  <si>
+    <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.600-1.pdf</t>
+  </si>
+  <si>
+    <t>Model Risk Management in the Era of Generative AI: Challenges, Opportunities, and Future Directions</t>
+  </si>
+  <si>
+    <t>https://www.preprints.org/manuscript/202503.1579/v1</t>
+  </si>
+  <si>
+    <t>Model Risk Management in the Era of Generative AI</t>
+  </si>
+  <si>
+    <t>Generative AI in finance: risks and potential solutions</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/publication/379389815_Generative_AI_in_finance_risks_and_potential_solutions</t>
+  </si>
+  <si>
+    <t>Provides a practical solution for evaluating LLMs using the LLM-as-a-Judge approach with Amazon Bedrock.</t>
   </si>
 </sst>
 </file>
@@ -2322,7 +2354,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -2638,19 +2670,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="hair">
@@ -2929,7 +2948,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3061,77 +3080,86 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3172,13 +3200,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3187,44 +3227,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3566,39 +3573,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8247B615-B3E9-494F-803D-FDE51FA53DC7}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" s="19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3609,34 +3616,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A699801B-B47A-4218-B52C-72C6572E2E88}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="40.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="17.25" x14ac:dyDescent="0.45">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="1" customFormat="1" ht="83.25" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -3647,10 +3654,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="1" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="1" customFormat="1" ht="83.25" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -3661,15 +3668,15 @@
         <v>6</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="1" customFormat="1" ht="41.65" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>8</v>
@@ -3678,58 +3685,58 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
-        <v>129</v>
+    <row r="6" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A6" s="77" t="s">
+        <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="71" t="s">
-        <v>138</v>
+      <c r="C6" s="74" t="s">
+        <v>137</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="75"/>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A7" s="78"/>
       <c r="B7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="72"/>
+      <c r="C7" s="75"/>
       <c r="D7" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="75"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A8" s="78"/>
       <c r="B8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="72"/>
+      <c r="C8" s="75"/>
       <c r="D8" s="9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="75"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A9" s="78"/>
       <c r="B9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="72"/>
+      <c r="C9" s="75"/>
       <c r="D9" s="9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="79"/>
       <c r="B10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="73"/>
+      <c r="C10" s="76"/>
       <c r="D10" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3744,19 +3751,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA809F9-C223-4554-BAE2-1EEE93FD3617}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="36.140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="36.1328125" style="5" customWidth="1"/>
     <col min="2" max="2" width="84" style="5" customWidth="1"/>
     <col min="3" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="19.899999999999999" x14ac:dyDescent="0.4">
       <c r="A1" s="25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.4">
       <c r="A2" s="21" t="s">
         <v>11</v>
       </c>
@@ -3764,21 +3771,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+    <row r="3" spans="1:2" ht="17.649999999999999" x14ac:dyDescent="0.4">
+      <c r="A3" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="79"/>
-    </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="82"/>
+    </row>
+    <row r="4" spans="1:2" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -3786,15 +3793,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="138.75" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -3802,7 +3809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
@@ -3810,13 +3817,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="77" t="s">
+    <row r="9" spans="1:2" ht="17.649999999999999" x14ac:dyDescent="0.4">
+      <c r="A9" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="78"/>
-    </row>
-    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B9" s="81"/>
+    </row>
+    <row r="10" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
@@ -3824,7 +3831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
@@ -3832,15 +3839,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="111" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>27</v>
       </c>
@@ -3848,7 +3855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -3856,7 +3863,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>31</v>
       </c>
@@ -3864,7 +3871,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="10"/>
     </row>
   </sheetData>
@@ -3879,21 +3886,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71EB1252-D75F-4826-9800-B45C9186BFB7}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.3984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="30.1328125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="35.59765625" style="4" customWidth="1"/>
     <col min="4" max="4" width="64" style="4" customWidth="1"/>
     <col min="5" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="52.15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
         <v>35</v>
       </c>
@@ -3904,143 +3911,143 @@
         <v>37</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="55.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="83" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="223.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="81"/>
+    <row r="4" spans="1:4" ht="207.4" x14ac:dyDescent="0.4">
+      <c r="A4" s="84"/>
       <c r="B4" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="69.400000000000006" x14ac:dyDescent="0.4">
+      <c r="A5" s="84"/>
+      <c r="B5" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D5" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="97.15" x14ac:dyDescent="0.4">
+      <c r="A6" s="84"/>
+      <c r="B6" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="69.400000000000006" x14ac:dyDescent="0.4">
+      <c r="A7" s="84"/>
+      <c r="B7" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="69.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="85"/>
+      <c r="B8" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="138.75" x14ac:dyDescent="0.4">
+      <c r="A9" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A6" s="81"/>
-      <c r="B6" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="81"/>
-      <c r="B7" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="82"/>
-      <c r="B8" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="11" t="s">
+    <row r="10" spans="1:4" ht="111" x14ac:dyDescent="0.4">
+      <c r="A10" s="84"/>
+      <c r="B10" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="A9" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="11" t="s">
+    <row r="11" spans="1:4" ht="97.15" x14ac:dyDescent="0.4">
+      <c r="A11" s="84"/>
+      <c r="B11" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A10" s="81"/>
-      <c r="B10" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="11" t="s">
+    <row r="12" spans="1:4" ht="388.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="84"/>
+      <c r="B12" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A11" s="81"/>
-      <c r="B11" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="81"/>
-      <c r="B12" s="9" t="s">
+    <row r="13" spans="1:4" ht="194.65" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="85"/>
+      <c r="B13" s="15" t="s">
         <v>163</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="225.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
-      <c r="B13" s="15" t="s">
-        <v>164</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>41</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -4055,93 +4062,93 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C121F933-0293-437A-91D0-197837E0FE6A}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="19.899999999999999" x14ac:dyDescent="0.4">
       <c r="A1" s="35" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.4">
       <c r="A2" s="30" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
       <c r="B3" s="36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B4" s="36" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="36" t="s">
+    <row r="5" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B5" s="36" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="36" t="s">
+    <row r="6" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B6" s="36" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="36" t="s">
+    <row r="7" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B7" s="36" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="36" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A8" s="37"/>
     </row>
-    <row r="9" spans="1:2" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="19.899999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="35" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.4">
       <c r="A10" s="38" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
       <c r="B11" s="36" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B12" s="36" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="36" t="s">
+    <row r="13" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B13" s="36" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
+    <row r="14" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B14" s="36" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="36" t="s">
+    <row r="15" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B15" s="36" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="36" t="s">
+    <row r="16" spans="1:2" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="B16" s="36" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A17" s="37"/>
     </row>
-    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A18" s="39" t="s">
         <v>44</v>
       </c>
@@ -4154,20 +4161,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0514BB9-9957-49F0-9837-F2CAB574058C}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="24.86328125" style="4" customWidth="1"/>
     <col min="2" max="2" width="28" style="4" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.265625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16.899999999999999" x14ac:dyDescent="0.4">
       <c r="A1" s="27" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="17.25" x14ac:dyDescent="0.45">
       <c r="A2" s="28" t="s">
         <v>46</v>
       </c>
@@ -4178,7 +4185,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="69.400000000000006" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
@@ -4186,10 +4193,10 @@
         <v>49</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="83.25" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>50</v>
       </c>
@@ -4197,10 +4204,10 @@
         <v>51</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>52</v>
       </c>
@@ -4208,10 +4215,10 @@
         <v>53</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="69.400000000000006" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>54</v>
       </c>
@@ -4219,10 +4226,10 @@
         <v>55</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="83.25" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>56</v>
       </c>
@@ -4230,10 +4237,10 @@
         <v>57</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="97.15" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>58</v>
       </c>
@@ -4241,15 +4248,15 @@
         <v>59</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="17" t="s">
         <v>62</v>
       </c>
@@ -4262,117 +4269,117 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07D5755-FD03-47AE-BEEC-A734A5ED5D4D}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="22.5" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.4">
       <c r="A3" s="30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B4" s="29" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B5" s="29" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B6" s="29" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B7" s="29" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="29" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B8" s="29" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="29" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B9" s="29" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="29" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A11" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="83"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="83"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="83"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A12" s="86"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A13" s="86"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A14" s="86"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A15" s="86"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4385,865 +4392,865 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C78623D-2E9A-4240-B89A-1E4117D4358D}">
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="32" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" style="32" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="32" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="32" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" style="32" customWidth="1"/>
-    <col min="8" max="8" width="65.42578125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="15.86328125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="21.1328125" style="32" customWidth="1"/>
+    <col min="3" max="3" width="15.86328125" style="32" customWidth="1"/>
+    <col min="4" max="4" width="18.3984375" style="32" customWidth="1"/>
+    <col min="5" max="5" width="15.86328125" style="32" customWidth="1"/>
+    <col min="6" max="6" width="18.86328125" style="32" customWidth="1"/>
+    <col min="7" max="7" width="28.265625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="65.3984375" style="32" customWidth="1"/>
     <col min="9" max="16384" width="9" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="19.899999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="34" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:8" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="1:8" ht="103.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="H3" s="61" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="97.15" x14ac:dyDescent="0.45">
+      <c r="A4" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>221</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="83.25" x14ac:dyDescent="0.45">
+      <c r="A5" s="90"/>
+      <c r="B5" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="H5" s="54" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="111" x14ac:dyDescent="0.45">
+      <c r="A6" s="90"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="G6" s="54" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6" s="54" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="111.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="91"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="56" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="56" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="A4" s="86" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="54" t="s">
+    <row r="8" spans="1:8" ht="69.400000000000006" x14ac:dyDescent="0.45">
+      <c r="A8" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>327</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="54" t="s">
-        <v>222</v>
-      </c>
-      <c r="G4" s="56" t="s">
-        <v>226</v>
-      </c>
-      <c r="H4" s="56" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="57" t="s">
-        <v>212</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="58" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="58" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A6" s="87"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57" t="s">
-        <v>215</v>
-      </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57" t="s">
-        <v>220</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>224</v>
-      </c>
-      <c r="G6" s="58" t="s">
-        <v>228</v>
-      </c>
-      <c r="H6" s="58" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59" t="s">
-        <v>221</v>
-      </c>
-      <c r="F7" s="59" t="s">
-        <v>225</v>
-      </c>
-      <c r="G7" s="60" t="s">
-        <v>229</v>
-      </c>
-      <c r="H7" s="60" t="s">
+      <c r="E8" s="62" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="64" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="94" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="66" t="s">
-        <v>328</v>
-      </c>
-      <c r="C8" s="67" t="s">
+    <row r="9" spans="1:8" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="90"/>
+      <c r="B9" s="87" t="s">
         <v>329</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="C9" s="57" t="s">
+        <v>381</v>
+      </c>
+      <c r="D9" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E9" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F9" s="53" t="s">
         <v>236</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G9" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="H8" s="68" t="s">
+      <c r="H9" s="54" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="87"/>
-      <c r="B9" s="84" t="s">
+    <row r="10" spans="1:8" ht="55.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="91"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="58" t="s">
+        <v>380</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="88"/>
+      <c r="F10" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="H10" s="69" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="69.400000000000006" x14ac:dyDescent="0.45">
+      <c r="A11" s="89" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>244</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="H11" s="70" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="69.400000000000006" x14ac:dyDescent="0.45">
+      <c r="A12" s="90"/>
+      <c r="B12" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="70" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="152.65" x14ac:dyDescent="0.45">
+      <c r="A13" s="90"/>
+      <c r="B13" s="53" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="59" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>257</v>
+      </c>
+      <c r="H13" s="70" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="40.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="91"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="H14" s="70" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="83.25" x14ac:dyDescent="0.45">
+      <c r="A15" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>265</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="69.400000000000006" x14ac:dyDescent="0.45">
+      <c r="A16" s="90"/>
+      <c r="B16" s="92" t="s">
+        <v>266</v>
+      </c>
+      <c r="C16" s="94" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="E16" s="92" t="s">
+        <v>269</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="G16" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="H16" s="70" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="83.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="91"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="G17" s="71" t="s">
+        <v>273</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="89" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>274</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="E18" s="96" t="s">
+        <v>277</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>278</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>279</v>
+      </c>
+      <c r="H18" s="70" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A19" s="90"/>
+      <c r="B19" s="87" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" s="87" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="87" t="s">
+        <v>282</v>
+      </c>
+      <c r="E19" s="92"/>
+      <c r="F19" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="G19" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="H19" s="70" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="91"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="G20" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="89" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>287</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>288</v>
+      </c>
+      <c r="D21" s="96" t="s">
+        <v>289</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>292</v>
+      </c>
+      <c r="H21" s="70" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A22" s="90"/>
+      <c r="B22" s="87" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="87" t="s">
+        <v>294</v>
+      </c>
+      <c r="D22" s="92"/>
+      <c r="E22" s="87" t="s">
+        <v>295</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>296</v>
+      </c>
+      <c r="G22" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="H22" s="70" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="91"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="G23" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="H23" s="70" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="41.65" x14ac:dyDescent="0.45">
+      <c r="A24" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>300</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="H24" s="70" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="69.400000000000006" x14ac:dyDescent="0.45">
+      <c r="A25" s="90"/>
+      <c r="B25" s="87" t="s">
+        <v>306</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>307</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="E25" s="87" t="s">
+        <v>309</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="G25" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="H25" s="70" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="69.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="91"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="55" t="s">
+        <v>312</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>313</v>
+      </c>
+      <c r="E26" s="88"/>
+      <c r="F26" s="55" t="s">
+        <v>314</v>
+      </c>
+      <c r="G26" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="H26" s="70" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A27" s="89" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>321</v>
+      </c>
+      <c r="H27" s="70" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A28" s="90"/>
+      <c r="B28" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>324</v>
+      </c>
+      <c r="E28" s="87" t="s">
+        <v>325</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>326</v>
+      </c>
+      <c r="G28" s="68" t="s">
         <v>330</v>
       </c>
-      <c r="C9" s="61" t="s">
-        <v>382</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>232</v>
-      </c>
-      <c r="E9" s="84" t="s">
-        <v>235</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>237</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>240</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="62" t="s">
-        <v>381</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="85"/>
-      <c r="F10" s="59" t="s">
-        <v>238</v>
-      </c>
-      <c r="G10" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="H10" s="97" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="86" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" s="54" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" s="54" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="G11" s="95" t="s">
-        <v>247</v>
-      </c>
-      <c r="H11" s="98" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="87"/>
-      <c r="B12" s="57" t="s">
-        <v>248</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>249</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>251</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>252</v>
-      </c>
-      <c r="G12" s="96" t="s">
-        <v>253</v>
-      </c>
-      <c r="H12" s="98" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A13" s="87"/>
-      <c r="B13" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="G13" s="96" t="s">
-        <v>258</v>
-      </c>
-      <c r="H13" s="98" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="64" t="s">
-        <v>259</v>
-      </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="99" t="s">
-        <v>260</v>
-      </c>
-      <c r="H14" s="98" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="86" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>261</v>
-      </c>
-      <c r="C15" s="55" t="s">
-        <v>262</v>
-      </c>
-      <c r="D15" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="F15" s="54" t="s">
-        <v>265</v>
-      </c>
-      <c r="G15" s="95" t="s">
-        <v>266</v>
-      </c>
-      <c r="H15" s="98" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="89" t="s">
-        <v>267</v>
-      </c>
-      <c r="C16" s="91" t="s">
-        <v>268</v>
-      </c>
-      <c r="D16" s="89" t="s">
-        <v>269</v>
-      </c>
-      <c r="E16" s="89" t="s">
-        <v>270</v>
-      </c>
-      <c r="F16" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="G16" s="96" t="s">
-        <v>272</v>
-      </c>
-      <c r="H16" s="98" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="59" t="s">
-        <v>273</v>
-      </c>
-      <c r="G17" s="99" t="s">
-        <v>274</v>
-      </c>
-      <c r="H17" s="98" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="86" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>276</v>
-      </c>
-      <c r="D18" s="54" t="s">
-        <v>277</v>
-      </c>
-      <c r="E18" s="93" t="s">
-        <v>278</v>
-      </c>
-      <c r="F18" s="54" t="s">
-        <v>279</v>
-      </c>
-      <c r="G18" s="95" t="s">
-        <v>280</v>
-      </c>
-      <c r="H18" s="98" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="87"/>
-      <c r="B19" s="84" t="s">
-        <v>281</v>
-      </c>
-      <c r="C19" s="84" t="s">
-        <v>282</v>
-      </c>
-      <c r="D19" s="84" t="s">
-        <v>283</v>
-      </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="57" t="s">
-        <v>284</v>
-      </c>
-      <c r="G19" s="96" t="s">
-        <v>285</v>
-      </c>
-      <c r="H19" s="98" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="59" t="s">
-        <v>286</v>
-      </c>
-      <c r="G20" s="99" t="s">
-        <v>287</v>
-      </c>
-      <c r="H20" s="98" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="86" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>288</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>289</v>
-      </c>
-      <c r="D21" s="93" t="s">
-        <v>290</v>
-      </c>
-      <c r="E21" s="54" t="s">
-        <v>291</v>
-      </c>
-      <c r="F21" s="54" t="s">
-        <v>292</v>
-      </c>
-      <c r="G21" s="95" t="s">
-        <v>293</v>
-      </c>
-      <c r="H21" s="98" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="87"/>
-      <c r="B22" s="84" t="s">
-        <v>294</v>
-      </c>
-      <c r="C22" s="84" t="s">
-        <v>295</v>
-      </c>
-      <c r="D22" s="89"/>
-      <c r="E22" s="84" t="s">
-        <v>296</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>297</v>
-      </c>
-      <c r="G22" s="96" t="s">
-        <v>298</v>
-      </c>
-      <c r="H22" s="98" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="59" t="s">
-        <v>299</v>
-      </c>
-      <c r="G23" s="99" t="s">
-        <v>300</v>
-      </c>
-      <c r="H23" s="98" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="86" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="54" t="s">
-        <v>301</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>302</v>
-      </c>
-      <c r="D24" s="54" t="s">
-        <v>303</v>
-      </c>
-      <c r="E24" s="54" t="s">
-        <v>304</v>
-      </c>
-      <c r="F24" s="54" t="s">
-        <v>305</v>
-      </c>
-      <c r="G24" s="95" t="s">
-        <v>306</v>
-      </c>
-      <c r="H24" s="98" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A25" s="87"/>
-      <c r="B25" s="84" t="s">
-        <v>307</v>
-      </c>
-      <c r="C25" s="63" t="s">
-        <v>308</v>
-      </c>
-      <c r="D25" s="57" t="s">
-        <v>309</v>
-      </c>
-      <c r="E25" s="84" t="s">
-        <v>310</v>
-      </c>
-      <c r="F25" s="57" t="s">
-        <v>311</v>
-      </c>
-      <c r="G25" s="96" t="s">
-        <v>312</v>
-      </c>
-      <c r="H25" s="98" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="59" t="s">
-        <v>313</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>314</v>
-      </c>
-      <c r="E26" s="85"/>
-      <c r="F26" s="59" t="s">
-        <v>315</v>
-      </c>
-      <c r="G26" s="99" t="s">
-        <v>316</v>
-      </c>
-      <c r="H26" s="98" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A27" s="86" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="54" t="s">
-        <v>317</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>318</v>
-      </c>
-      <c r="D27" s="54" t="s">
-        <v>319</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>320</v>
-      </c>
-      <c r="F27" s="54" t="s">
-        <v>321</v>
-      </c>
-      <c r="G27" s="95" t="s">
-        <v>322</v>
-      </c>
-      <c r="H27" s="98" t="s">
+      <c r="H28" s="70" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A28" s="87"/>
-      <c r="B28" s="57" t="s">
-        <v>323</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>324</v>
-      </c>
-      <c r="D28" s="57" t="s">
-        <v>325</v>
-      </c>
-      <c r="E28" s="84" t="s">
-        <v>326</v>
-      </c>
-      <c r="F28" s="57" t="s">
-        <v>327</v>
-      </c>
-      <c r="G28" s="96" t="s">
+    <row r="29" spans="1:8" ht="55.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="91"/>
+      <c r="B29" s="55" t="s">
         <v>331</v>
       </c>
-      <c r="H28" s="98" t="s">
+      <c r="C29" s="55"/>
+      <c r="D29" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="E29" s="88"/>
+      <c r="F29" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="G29" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="H29" s="70" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
-      <c r="B29" s="59" t="s">
-        <v>332</v>
-      </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59" t="s">
-        <v>333</v>
-      </c>
-      <c r="E29" s="85"/>
-      <c r="F29" s="59" t="s">
-        <v>334</v>
-      </c>
-      <c r="G29" s="99" t="s">
+    <row r="30" spans="1:8" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A30" s="89" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="H29" s="98" t="s">
+      <c r="C30" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>338</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="G30" s="67" t="s">
+        <v>340</v>
+      </c>
+      <c r="H30" s="70" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="86" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="54" t="s">
-        <v>336</v>
-      </c>
-      <c r="C30" s="54" t="s">
-        <v>337</v>
-      </c>
-      <c r="D30" s="54" t="s">
-        <v>338</v>
-      </c>
-      <c r="E30" s="54" t="s">
-        <v>339</v>
-      </c>
-      <c r="F30" s="54" t="s">
-        <v>340</v>
-      </c>
-      <c r="G30" s="95" t="s">
+    <row r="31" spans="1:8" ht="55.5" x14ac:dyDescent="0.45">
+      <c r="A31" s="90"/>
+      <c r="B31" s="87" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="98" t="s">
+      <c r="C31" s="87" t="s">
+        <v>342</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="E31" s="87" t="s">
+        <v>344</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>345</v>
+      </c>
+      <c r="G31" s="68" t="s">
+        <v>346</v>
+      </c>
+      <c r="H31" s="70" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31" s="87"/>
-      <c r="B31" s="84" t="s">
-        <v>342</v>
-      </c>
-      <c r="C31" s="84" t="s">
-        <v>343</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="E31" s="84" t="s">
-        <v>345</v>
-      </c>
-      <c r="F31" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="G31" s="96" t="s">
+    <row r="32" spans="1:8" ht="69.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="91"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="55" t="s">
         <v>347</v>
       </c>
-      <c r="H31" s="98" t="s">
+      <c r="E32" s="88"/>
+      <c r="F32" s="55" t="s">
+        <v>348</v>
+      </c>
+      <c r="G32" s="71" t="s">
+        <v>349</v>
+      </c>
+      <c r="H32" s="70" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="88"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="59" t="s">
-        <v>348</v>
-      </c>
-      <c r="E32" s="85"/>
-      <c r="F32" s="59" t="s">
-        <v>349</v>
-      </c>
-      <c r="G32" s="99" t="s">
+    <row r="33" spans="1:8" ht="111" x14ac:dyDescent="0.45">
+      <c r="A33" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="H32" s="98" t="s">
+      <c r="C33" s="50" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="G33" s="67" t="s">
+        <v>355</v>
+      </c>
+      <c r="H33" s="70" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="150" x14ac:dyDescent="0.25">
-      <c r="A33" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="54" t="s">
-        <v>351</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="D33" s="54" t="s">
-        <v>353</v>
-      </c>
-      <c r="E33" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="F33" s="54" t="s">
-        <v>355</v>
-      </c>
-      <c r="G33" s="95" t="s">
+    <row r="34" spans="1:8" ht="97.15" x14ac:dyDescent="0.45">
+      <c r="A34" s="90"/>
+      <c r="B34" s="87" t="s">
         <v>356</v>
       </c>
-      <c r="H33" s="98" t="s">
+      <c r="C34" s="87" t="s">
+        <v>357</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>358</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>359</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>360</v>
+      </c>
+      <c r="G34" s="68" t="s">
+        <v>361</v>
+      </c>
+      <c r="H34" s="70" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A34" s="87"/>
-      <c r="B34" s="84" t="s">
-        <v>357</v>
-      </c>
-      <c r="C34" s="84" t="s">
-        <v>358</v>
-      </c>
-      <c r="D34" s="57" t="s">
-        <v>359</v>
-      </c>
-      <c r="E34" s="57" t="s">
-        <v>360</v>
-      </c>
-      <c r="F34" s="57" t="s">
-        <v>361</v>
-      </c>
-      <c r="G34" s="96" t="s">
+    <row r="35" spans="1:8" ht="69.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="91"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="55" t="s">
         <v>362</v>
       </c>
-      <c r="H34" s="98" t="s">
+      <c r="E35" s="55" t="s">
+        <v>363</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>364</v>
+      </c>
+      <c r="G35" s="71" t="s">
+        <v>365</v>
+      </c>
+      <c r="H35" s="70" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="88"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="59" t="s">
-        <v>363</v>
-      </c>
-      <c r="E35" s="59" t="s">
-        <v>364</v>
-      </c>
-      <c r="F35" s="59" t="s">
-        <v>365</v>
-      </c>
-      <c r="G35" s="99" t="s">
+    <row r="36" spans="1:8" ht="83.25" x14ac:dyDescent="0.45">
+      <c r="A36" s="89" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="50" t="s">
         <v>366</v>
       </c>
-      <c r="H35" s="98" t="s">
+      <c r="C36" s="50" t="s">
+        <v>367</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>368</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>369</v>
+      </c>
+      <c r="F36" s="50" t="s">
+        <v>370</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>371</v>
+      </c>
+      <c r="H36" s="70" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A36" s="86" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36" s="54" t="s">
-        <v>367</v>
-      </c>
-      <c r="C36" s="54" t="s">
-        <v>368</v>
-      </c>
-      <c r="D36" s="54" t="s">
-        <v>369</v>
-      </c>
-      <c r="E36" s="54" t="s">
-        <v>370</v>
-      </c>
-      <c r="F36" s="54" t="s">
-        <v>371</v>
-      </c>
-      <c r="G36" s="95" t="s">
+    <row r="37" spans="1:8" ht="69.400000000000006" x14ac:dyDescent="0.45">
+      <c r="A37" s="90"/>
+      <c r="B37" s="87" t="s">
         <v>372</v>
       </c>
-      <c r="H36" s="98" t="s">
+      <c r="C37" s="87" t="s">
+        <v>373</v>
+      </c>
+      <c r="D37" s="87" t="s">
+        <v>374</v>
+      </c>
+      <c r="E37" s="87" t="s">
+        <v>375</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>376</v>
+      </c>
+      <c r="G37" s="68" t="s">
+        <v>377</v>
+      </c>
+      <c r="H37" s="70" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A37" s="87"/>
-      <c r="B37" s="84" t="s">
-        <v>373</v>
-      </c>
-      <c r="C37" s="84" t="s">
-        <v>374</v>
-      </c>
-      <c r="D37" s="84" t="s">
-        <v>375</v>
-      </c>
-      <c r="E37" s="84" t="s">
-        <v>376</v>
-      </c>
-      <c r="F37" s="57" t="s">
-        <v>377</v>
-      </c>
-      <c r="G37" s="96" t="s">
+    <row r="38" spans="1:8" ht="42" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="91"/>
+      <c r="B38" s="88"/>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
+      <c r="E38" s="88"/>
+      <c r="F38" s="55" t="s">
         <v>378</v>
       </c>
-      <c r="H37" s="98" t="s">
+      <c r="G38" s="71" t="s">
+        <v>379</v>
+      </c>
+      <c r="H38" s="70" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="88"/>
-      <c r="B38" s="85"/>
-      <c r="C38" s="85"/>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="59" t="s">
-        <v>379</v>
-      </c>
-      <c r="G38" s="99" t="s">
-        <v>380</v>
-      </c>
-      <c r="H38" s="98" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="16.899999999999999" x14ac:dyDescent="0.45">
       <c r="A40" s="33" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="31" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A42" s="31" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="31" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A43" s="31" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A44" s="31" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A45" s="31" t="s">
         <v>209</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="31" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5292,337 +5299,397 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13721B4F-9D60-4281-A9AC-563305380FB2}">
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="39.85546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="52.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.86328125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="39.86328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="52.59765625" style="4" customWidth="1"/>
     <col min="5" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="40" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="41" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>398</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="C2" s="42" t="s">
         <v>399</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="D2" s="43" t="s">
         <v>400</v>
       </c>
-      <c r="D2" s="43" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A3" s="44">
         <v>1</v>
       </c>
       <c r="B3" s="45" t="s">
+        <v>438</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>438</v>
+      </c>
+      <c r="D3" s="72" t="s">
         <v>439</v>
       </c>
-      <c r="C3" s="45" t="s">
-        <v>439</v>
-      </c>
-      <c r="D3" s="100" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A4" s="44">
         <v>2</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>92</v>
+        <v>442</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
+        <v>441</v>
+      </c>
+      <c r="D4" s="72" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
+      <c r="A5" s="44">
         <v>3</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>390</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>384</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B5" s="45" t="s">
+        <v>445</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>444</v>
+      </c>
+      <c r="D5" s="72" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A6" s="44">
         <v>4</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>391</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B6" s="45" t="s">
+        <v>449</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>447</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A7" s="44">
         <v>5</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>385</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="47">
+      <c r="B7" s="45" t="s">
+        <v>450</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>450</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
+      <c r="A8" s="44">
         <v>6</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>402</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="B8" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>452</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A9" s="44">
         <v>7</v>
       </c>
-      <c r="B9" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="165" x14ac:dyDescent="0.25">
+      <c r="B9" s="48" t="s">
+        <v>389</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>383</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A10" s="44">
         <v>8</v>
       </c>
-      <c r="B10" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="47">
+      <c r="B10" s="48" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="55.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="44">
         <v>9</v>
       </c>
-      <c r="B11" s="49" t="s">
-        <v>392</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>384</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A12" s="44">
         <v>10</v>
       </c>
-      <c r="B12" s="51" t="s">
-        <v>387</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>387</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="B12" s="48" t="s">
+        <v>401</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A13" s="44">
         <v>11</v>
       </c>
-      <c r="B13" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="47">
+      <c r="B13" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="124.9" x14ac:dyDescent="0.4">
+      <c r="A14" s="44">
         <v>12</v>
       </c>
-      <c r="B14" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B14" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A15" s="44">
         <v>13</v>
       </c>
-      <c r="B15" s="51" t="s">
-        <v>394</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="48" t="s">
+        <v>391</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>385</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A16" s="44">
         <v>14</v>
       </c>
-      <c r="B16" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="50" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="47">
+      <c r="B16" s="48" t="s">
+        <v>386</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>386</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="83.25" x14ac:dyDescent="0.4">
+      <c r="A17" s="44">
         <v>15</v>
       </c>
-      <c r="B17" s="51" t="s">
-        <v>395</v>
-      </c>
-      <c r="C17" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B17" s="48" t="s">
+        <v>392</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="55.5" x14ac:dyDescent="0.4">
       <c r="A18" s="44">
         <v>16</v>
       </c>
-      <c r="B18" s="51" t="s">
-        <v>396</v>
-      </c>
-      <c r="C18" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" s="50" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="B18" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A19" s="44">
         <v>17</v>
       </c>
-      <c r="B19" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="50" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="47">
+      <c r="B19" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="A20" s="44">
         <v>18</v>
       </c>
-      <c r="B20" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="50" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="B20" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A21" s="44">
         <v>19</v>
       </c>
-      <c r="B21" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>388</v>
-      </c>
-      <c r="D21" s="50" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
       <c r="A22" s="44">
         <v>20</v>
       </c>
-      <c r="B22" s="101" t="s">
-        <v>397</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>389</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>128</v>
+      <c r="B22" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="55.5" x14ac:dyDescent="0.4">
+      <c r="A23" s="44">
+        <v>21</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="41.65" x14ac:dyDescent="0.4">
+      <c r="A24" s="44">
+        <v>22</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="69.400000000000006" x14ac:dyDescent="0.4">
+      <c r="A25" s="44">
+        <v>23</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="83.65" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="44">
+        <v>24</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>396</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>388</v>
+      </c>
+      <c r="D26" s="73" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{AF3CDD14-31C6-483B-B808-8B69B30FA7A2}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{1FCA6D59-83B4-4756-B201-548D4BAD4C28}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{11ABF1E5-65B9-44BD-9F33-C7AEDE9D7501}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{CDC39422-DB82-4AB4-81F7-4380DBA11EDE}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{E8264F34-E863-45D8-A0C4-14110923CECE}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{645EAF52-AE6D-449D-8453-1EFD31E07BFA}"/>
-    <hyperlink ref="D10" r:id="rId7" display="https://openreview.net/pdf?id=goFpCuJalN" xr:uid="{B75AA544-47D8-4702-A50B-8827854B73E5}"/>
-    <hyperlink ref="D11" r:id="rId8" xr:uid="{D1E2B633-F039-4789-AEE9-AECC35D20E2F}"/>
-    <hyperlink ref="D12" r:id="rId9" xr:uid="{AD2F3D29-8AFA-487E-B872-E27D78AA5626}"/>
-    <hyperlink ref="D13" r:id="rId10" xr:uid="{E766DE2D-3799-4DD8-A517-4C732BD3F992}"/>
-    <hyperlink ref="D14" r:id="rId11" xr:uid="{7E2ECC03-075F-499F-891F-FD461C343BD7}"/>
-    <hyperlink ref="D15" r:id="rId12" xr:uid="{EB390FB3-06BE-4CE5-B1A2-11A2B252950C}"/>
-    <hyperlink ref="D16" r:id="rId13" xr:uid="{8152D252-4E3C-402F-AC9D-1B50D9CC1109}"/>
-    <hyperlink ref="D17" r:id="rId14" xr:uid="{9202F715-B00A-4FEF-B885-A95BAA7DE4F2}"/>
-    <hyperlink ref="D18" r:id="rId15" xr:uid="{B15F3750-7B9F-4E15-A1C4-2269BE01B7DD}"/>
-    <hyperlink ref="D19" r:id="rId16" xr:uid="{F72B9FB5-1EB0-4DDA-82E4-D461BD979007}"/>
-    <hyperlink ref="D20" r:id="rId17" xr:uid="{ACB6CD04-A28F-481D-A55B-3E6F93A34D1E}"/>
-    <hyperlink ref="D21" r:id="rId18" xr:uid="{E3EFB99D-D3F2-40DE-A3CD-8988EB17C755}"/>
-    <hyperlink ref="D22" r:id="rId19" xr:uid="{99410DF8-1E0E-4E36-AEC1-1AB499DF9D0D}"/>
+    <hyperlink ref="D8" r:id="rId1" xr:uid="{AF3CDD14-31C6-483B-B808-8B69B30FA7A2}"/>
+    <hyperlink ref="D9" r:id="rId2" xr:uid="{1FCA6D59-83B4-4756-B201-548D4BAD4C28}"/>
+    <hyperlink ref="D10" r:id="rId3" xr:uid="{11ABF1E5-65B9-44BD-9F33-C7AEDE9D7501}"/>
+    <hyperlink ref="D11" r:id="rId4" xr:uid="{CDC39422-DB82-4AB4-81F7-4380DBA11EDE}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{E8264F34-E863-45D8-A0C4-14110923CECE}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{645EAF52-AE6D-449D-8453-1EFD31E07BFA}"/>
+    <hyperlink ref="D14" r:id="rId7" display="https://openreview.net/pdf?id=goFpCuJalN" xr:uid="{B75AA544-47D8-4702-A50B-8827854B73E5}"/>
+    <hyperlink ref="D15" r:id="rId8" xr:uid="{D1E2B633-F039-4789-AEE9-AECC35D20E2F}"/>
+    <hyperlink ref="D16" r:id="rId9" xr:uid="{AD2F3D29-8AFA-487E-B872-E27D78AA5626}"/>
+    <hyperlink ref="D17" r:id="rId10" xr:uid="{E766DE2D-3799-4DD8-A517-4C732BD3F992}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{7E2ECC03-075F-499F-891F-FD461C343BD7}"/>
+    <hyperlink ref="D19" r:id="rId12" xr:uid="{EB390FB3-06BE-4CE5-B1A2-11A2B252950C}"/>
+    <hyperlink ref="D20" r:id="rId13" xr:uid="{8152D252-4E3C-402F-AC9D-1B50D9CC1109}"/>
+    <hyperlink ref="D21" r:id="rId14" xr:uid="{9202F715-B00A-4FEF-B885-A95BAA7DE4F2}"/>
+    <hyperlink ref="D22" r:id="rId15" xr:uid="{B15F3750-7B9F-4E15-A1C4-2269BE01B7DD}"/>
+    <hyperlink ref="D23" r:id="rId16" xr:uid="{F72B9FB5-1EB0-4DDA-82E4-D461BD979007}"/>
+    <hyperlink ref="D24" r:id="rId17" xr:uid="{ACB6CD04-A28F-481D-A55B-3E6F93A34D1E}"/>
+    <hyperlink ref="D25" r:id="rId18" xr:uid="{E3EFB99D-D3F2-40DE-A3CD-8988EB17C755}"/>
+    <hyperlink ref="D26" r:id="rId19" xr:uid="{99410DF8-1E0E-4E36-AEC1-1AB499DF9D0D}"/>
     <hyperlink ref="D3" r:id="rId20" xr:uid="{3248F75B-5794-4785-A0C6-E1997968B282}"/>
+    <hyperlink ref="D4" r:id="rId21" xr:uid="{0DE626B0-2018-4881-8E70-5FF4DDF4F44C}"/>
+    <hyperlink ref="D5" r:id="rId22" xr:uid="{B1B0E218-D387-4C7A-B546-A415B7F1204D}"/>
+    <hyperlink ref="D6" r:id="rId23" xr:uid="{EAEEC302-23B3-4D68-9486-D650AE31D364}"/>
+    <hyperlink ref="D7" r:id="rId24" xr:uid="{C9B93549-493E-4D1E-A413-17ECF2375A2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
